--- a/results/02_taxa_assemblage/LDA_Method/ModelS_XSupport/tables/cross_support_site_predictions.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelS_XSupport/tables/cross_support_site_predictions.xlsx
@@ -425,15 +425,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>StationID</t>
-        </is>
-      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Original_Cluster</t>
@@ -473,7 +468,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>004ABC</t>
+          <t>DR-03</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -481,37 +476,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8711690313982517</v>
+        <v>0.4914004173276788</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1106877979123835</v>
+        <v>1.76298911609951e-21</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0181431706893647</v>
+        <v>0.5085995826723212</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>010B</t>
+          <t>DR-10</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,19 +516,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4494793559583735</v>
+        <v>4.098311769095971e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.850908566288664e-05</v>
+        <v>1.389305986185035e-13</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5505021349559636</v>
+        <v>0.9999999590167433</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>011A</t>
+          <t>DR-54</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -551,49 +546,49 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3235681196957009</v>
+        <v>2.010106612071253e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002916811157976414</v>
+        <v>1.548740374912976e-16</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6735150691463226</v>
+        <v>0.9999979898933877</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>016C</t>
+          <t>DR-163</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7992675997067096</v>
+        <v>8.661513651670974e-32</v>
       </c>
       <c r="G5" t="n">
-        <v>1.373821357853867e-05</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2007186620797119</v>
+        <v>3.271755151167421e-17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>026C</t>
+          <t>DR-164</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -611,109 +606,109 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00836434685723909</v>
+        <v>4.188245128938946e-42</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9890230215271709</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002612631615590071</v>
+        <v>5.765329706443533e-24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>030ABC</t>
+          <t>DR-167</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>8.879276523289411e-07</v>
+        <v>1.552559975159302e-29</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9999990339835166</v>
+        <v>0.9999999999999027</v>
       </c>
       <c r="H7" t="n">
-        <v>7.808883099327338e-08</v>
+        <v>9.733214621016334e-14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>033ABC</t>
+          <t>DR-168</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.006978757123890844</v>
+        <v>2.741206003103437e-38</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9904446089285911</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002576633947518036</v>
+        <v>6.813549918722915e-22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>035C</t>
+          <t>DR-175</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>4.119111423094613e-07</v>
+        <v>6.712395074666319e-31</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9999995646986414</v>
+        <v>0.9999999999999725</v>
       </c>
       <c r="H9" t="n">
-        <v>2.339021633336265e-08</v>
+        <v>2.743268276460132e-14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>036C</t>
+          <t>DR-195</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -721,149 +716,149 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0003620298644050648</v>
+        <v>0.9995526880205594</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9994948776725275</v>
+        <v>6.905400780465352e-45</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0001430924630675426</v>
+        <v>0.000447311979440594</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>DR-197</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.002660900360722133</v>
+        <v>2.242107158608158e-08</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9971060151655772</v>
+        <v>6.625979709576053e-11</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0002330844737008179</v>
+        <v>0.9999999775126686</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>DR-202</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0008740448592348439</v>
+        <v>3.061297653740543e-05</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9990905847484745</v>
+        <v>2.487595470297807e-16</v>
       </c>
       <c r="H12" t="n">
-        <v>3.537039229063912e-05</v>
+        <v>0.9999693870234623</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>DR-204</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9308010431704465</v>
+        <v>5.173938765476805e-07</v>
       </c>
       <c r="G13" t="n">
-        <v>6.174869961613486e-06</v>
+        <v>1.34074020420173e-14</v>
       </c>
       <c r="H13" t="n">
-        <v>0.06919278195959194</v>
+        <v>0.9999994826061099</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>DR-205</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6116801065997893</v>
+        <v>0.0004766501040335004</v>
       </c>
       <c r="G14" t="n">
-        <v>3.711260240836151e-07</v>
+        <v>9.499084300941895e-24</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3883195222741865</v>
+        <v>0.9995233498959665</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>DR-206</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -871,63 +866,63 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5287840691012985</v>
+        <v>1.039839269974045e-16</v>
       </c>
       <c r="G15" t="n">
-        <v>0.07405375053826374</v>
+        <v>0.9992839879545359</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3971621803604378</v>
+        <v>0.0007160120454640274</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>DR-207</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.00434672916813738</v>
+        <v>0.9999829829335232</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9910411929109547</v>
+        <v>1.460641766532878e-48</v>
       </c>
       <c r="H16" t="n">
-        <v>0.004612077920907683</v>
+        <v>1.701706647690897e-05</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>DR-208</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -935,29 +930,29 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2991889492749532</v>
+        <v>6.090220025578483e-06</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4352211723755948</v>
+        <v>2.819620327627155e-20</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2655898783494521</v>
+        <v>0.9999939097799744</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>DR-209</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -965,85 +960,85 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" t="b">
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0105653863090689</v>
+        <v>0.0004537031833414897</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9893360331645505</v>
+        <v>6.399441533796586e-24</v>
       </c>
       <c r="H18" t="n">
-        <v>9.85805263805592e-05</v>
+        <v>0.9995462968166585</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t>DR-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7871024560842821</v>
+        <v>0.0006132722338878922</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0003357831302574726</v>
+        <v>2.10242000719677e-22</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2125617607854604</v>
+        <v>0.9993867277661121</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>DR-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" t="b">
         <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8724838535943112</v>
+        <v>4.452045330423855e-09</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1067157255526522</v>
+        <v>3.624817801607503e-07</v>
       </c>
       <c r="H20" t="n">
-        <v>0.02080042085303651</v>
+        <v>0.9999996330661746</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>DR-18</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1051,7 +1046,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1061,49 +1056,49 @@
         <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9538486601068155</v>
+        <v>0.9811234885426894</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0004705190173690836</v>
+        <v>1.898841446727086e-36</v>
       </c>
       <c r="H21" t="n">
-        <v>0.04568082087581546</v>
+        <v>0.01887651145731052</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>DR-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" t="b">
         <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>0.00252833182742124</v>
+        <v>0.3652250162064756</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9973005409515686</v>
+        <v>1.171446580014517e-26</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0001711272210100248</v>
+        <v>0.6347749837935245</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>DR-20</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1111,29 +1106,29 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6939071164967441</v>
+        <v>0.0002779462404193438</v>
       </c>
       <c r="G23" t="n">
-        <v>8.566065000124497e-06</v>
+        <v>1.750992354023995e-17</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3060843174382558</v>
+        <v>0.9997220537595806</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>DR-23</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1141,33 +1136,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7549841585034729</v>
+        <v>8.408178932678543e-07</v>
       </c>
       <c r="G24" t="n">
-        <v>4.125058893763906e-06</v>
+        <v>2.045946738789998e-14</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2450117164376333</v>
+        <v>0.9999991591820863</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>DR-38</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1175,25 +1170,25 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" t="b">
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>0.02956497089645847</v>
+        <v>0.999999599309811</v>
       </c>
       <c r="G25" t="n">
-        <v>3.413384498961783e-12</v>
+        <v>2.433602805658487e-51</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9704350291001282</v>
+        <v>4.006901890331989e-07</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>DR-40</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1201,33 +1196,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4161782956845052</v>
+        <v>0.9434858434122564</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0004498456430531582</v>
+        <v>3.4861163351444e-32</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5833718586724417</v>
+        <v>0.05651415658774357</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>DR-44</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1235,25 +1230,25 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E27" t="b">
         <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8103868194386609</v>
+        <v>0.07829304867839018</v>
       </c>
       <c r="G27" t="n">
-        <v>1.757922826634908e-05</v>
+        <v>1.097069786508977e-28</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1895956013330727</v>
+        <v>0.9217069513216098</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>DR-45</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1261,7 +1256,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1271,49 +1266,49 @@
         <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7302343920852582</v>
+        <v>0.9994961593998823</v>
       </c>
       <c r="G28" t="n">
-        <v>0.001481074934505133</v>
+        <v>5.507451050981829e-41</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2682845329802366</v>
+        <v>0.0005038406001176753</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>DR-48</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4207278417688977</v>
+        <v>0.0008733383837855163</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5276328216873344</v>
+        <v>2.789955739355438e-22</v>
       </c>
       <c r="H29" t="n">
-        <v>0.05163933654376802</v>
+        <v>0.9991266616162144</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>DR-49</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1321,7 +1316,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1331,53 +1326,53 @@
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8044505191968531</v>
+        <v>0.9098973748970235</v>
       </c>
       <c r="G30" t="n">
-        <v>6.259176395381748e-06</v>
+        <v>6.443919329298773e-33</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1955432216267514</v>
+        <v>0.09010262510297665</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>DR-50</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E31" t="b">
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8666066385420147</v>
+        <v>0.05670444379523303</v>
       </c>
       <c r="G31" t="n">
-        <v>4.267764210714554e-05</v>
+        <v>2.884218623747994e-25</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1333506838158781</v>
+        <v>0.943295556204767</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>DR-51</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1385,29 +1380,29 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E32" t="b">
         <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8898392027966718</v>
+        <v>4.922783384216739e-05</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0002559406055330316</v>
+        <v>2.497697121293739e-17</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1099048565977951</v>
+        <v>0.9999507721661578</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>DR-53</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1415,25 +1410,25 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E33" t="b">
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9847790517853618</v>
+        <v>0.002690981243843975</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0002630302995705633</v>
+        <v>5.35945526971653e-22</v>
       </c>
       <c r="H33" t="n">
-        <v>0.01495791791506759</v>
+        <v>0.9973090187561561</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>DR-55</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1451,19 +1446,19 @@
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4265403856791288</v>
+        <v>0.0001916344552161711</v>
       </c>
       <c r="G34" t="n">
-        <v>1.916154167729947e-08</v>
+        <v>9.342885039606009e-26</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5734595951593294</v>
+        <v>0.9998083655447838</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>DR-56</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1471,7 +1466,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1481,23 +1476,23 @@
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6320740459198534</v>
+        <v>0.8703391515563766</v>
       </c>
       <c r="G35" t="n">
-        <v>5.913042043695691e-07</v>
+        <v>6.080854167637393e-31</v>
       </c>
       <c r="H35" t="n">
-        <v>0.3679253627759423</v>
+        <v>0.1296608484436232</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>DR-59</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1505,25 +1500,25 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E36" t="b">
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>0.688595472134667</v>
+        <v>9.657027928612704e-07</v>
       </c>
       <c r="G36" t="n">
-        <v>1.264104573029356e-06</v>
+        <v>7.661194044044215e-14</v>
       </c>
       <c r="H36" t="n">
-        <v>0.3114032637607601</v>
+        <v>0.9999990342971306</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1531,7 +1526,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1541,49 +1536,49 @@
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6619306471382498</v>
+        <v>0.9998962976373398</v>
       </c>
       <c r="G37" t="n">
-        <v>9.07001518158315e-07</v>
+        <v>2.124781701632662e-52</v>
       </c>
       <c r="H37" t="n">
-        <v>0.338068445860232</v>
+        <v>0.000103702362660273</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>DR-140</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E38" t="b">
         <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5153704661804788</v>
+        <v>0.001473973451602997</v>
       </c>
       <c r="G38" t="n">
-        <v>2.47845269835088e-06</v>
+        <v>1.166376182036637e-21</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4846270553668228</v>
+        <v>0.9985260265483971</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1591,29 +1586,29 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6992980302945337</v>
+        <v>0.100788981938709</v>
       </c>
       <c r="G39" t="n">
-        <v>1.204305131126426e-05</v>
+        <v>1.388523814739045e-26</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3006899266541549</v>
+        <v>0.899211018061291</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1631,49 +1626,49 @@
         <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6876575289748045</v>
+        <v>0.9938703069845746</v>
       </c>
       <c r="G40" t="n">
-        <v>7.449283679858349e-07</v>
+        <v>5.893127491478644e-39</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3123417260968276</v>
+        <v>0.006129693015425484</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E41" t="b">
         <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>0.4753416092332927</v>
+        <v>0.9921625352196256</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0003194532995355824</v>
+        <v>2.810641108415308e-37</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5243389374671716</v>
+        <v>0.007837464780374458</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>DR-144</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1685,29 +1680,29 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2751104507008352</v>
+        <v>0.9999999999605622</v>
       </c>
       <c r="G42" t="n">
-        <v>3.775102224497596e-08</v>
+        <v>1.64577733998495e-58</v>
       </c>
       <c r="H42" t="n">
-        <v>0.7248895115481426</v>
+        <v>3.943772620685546e-11</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>DR-157</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1718,256 +1713,16 @@
         <v>3</v>
       </c>
       <c r="E43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3911552665643847</v>
+        <v>0.4133489369190837</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0001405052704865593</v>
+        <v>5.143367635951179e-28</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6087042281651288</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>S65</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaStrong</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" t="b">
-        <v>1</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.6513411500357786</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1.791000138026305e-06</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.3486570589640833</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>S69</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>3</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaWeak</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>3</v>
-      </c>
-      <c r="E45" t="b">
-        <v>1</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.3220774164611825</v>
-      </c>
-      <c r="G45" t="n">
-        <v>3.442844559751224e-08</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.6779225491103719</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>S70</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>3</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaWeak</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>3</v>
-      </c>
-      <c r="E46" t="b">
-        <v>1</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.4943312453440981</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0.0008420106970950544</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.5048267439588069</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>S72</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>3</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaStrong</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>3</v>
-      </c>
-      <c r="E47" t="b">
-        <v>1</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.3705987670689433</v>
-      </c>
-      <c r="G47" t="n">
-        <v>1.425658837052478e-05</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.6293869763426861</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>S74</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>3</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaStrong</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" t="b">
-        <v>0</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.5524346515423602</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.001643330312096585</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.4459220181455434</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>S79</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaStrong</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" t="b">
-        <v>1</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0.7867170917005086</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0.003182176260204515</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.2101007320392868</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaStrong</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" t="b">
-        <v>1</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0.6897568403512964</v>
-      </c>
-      <c r="G50" t="n">
-        <v>3.260956432677119e-05</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.3102105500843769</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>S81</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>EnvWeak_TaxaStrong</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" t="b">
-        <v>1</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0.9372751070725218</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0.0004370803562206253</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.06228781257125761</v>
+        <v>0.5866510630809163</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/LDA_Method/ModelS_XSupport/tables/cross_support_site_predictions.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelS_XSupport/tables/cross_support_site_predictions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,29 +476,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4914004173276788</v>
+        <v>0.998752729442381</v>
       </c>
       <c r="G2" t="n">
-        <v>1.76298911609951e-21</v>
+        <v>0.001247270557618951</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5085995826723212</v>
+        <v>9.474796039594086e-27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>DR-10</t>
+          <t>DR-94</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -510,59 +510,59 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>4.098311769095971e-08</v>
+        <v>0.8704088668453721</v>
       </c>
       <c r="G3" t="n">
-        <v>1.389305986185035e-13</v>
+        <v>0.0001944975811842939</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9999999590167433</v>
+        <v>0.1293966355734435</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>DR-54</t>
+          <t>DR-103</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>2.010106612071253e-06</v>
+        <v>0.0003761675276060683</v>
       </c>
       <c r="G4" t="n">
-        <v>1.548740374912976e-16</v>
+        <v>1.937770785980285e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9999979898933877</v>
+        <v>0.9996218947016079</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>DR-163</t>
+          <t>SCR-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -570,55 +570,55 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>8.661513651670974e-32</v>
+        <v>0.9964455835682403</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0.003554416431759609</v>
       </c>
       <c r="H5" t="n">
-        <v>3.271755151167421e-17</v>
+        <v>2.055349579375182e-32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>DR-164</t>
+          <t>SCR-02</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>4.188245128938946e-42</v>
+        <v>2.124234677395084e-34</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>1.106606378344374e-38</v>
       </c>
       <c r="H6" t="n">
-        <v>5.765329706443533e-24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>DR-167</t>
+          <t>LSC-07</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -626,59 +626,59 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1.552559975159302e-29</v>
+        <v>0.9386343260964012</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9999999999999027</v>
+        <v>0.06136567390359882</v>
       </c>
       <c r="H7" t="n">
-        <v>9.733214621016334e-14</v>
+        <v>2.843174666881501e-31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>DR-168</t>
+          <t>DR-125</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>2.741206003103437e-38</v>
+        <v>1.178100880455004e-14</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>9.306263433931688e-19</v>
       </c>
       <c r="H8" t="n">
-        <v>6.813549918722915e-22</v>
+        <v>0.9999999999999882</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>DR-175</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -686,29 +686,29 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>6.712395074666319e-31</v>
+        <v>1.015638210643479e-07</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9999999999999725</v>
+        <v>6.221921825830707e-11</v>
       </c>
       <c r="H9" t="n">
-        <v>2.743268276460132e-14</v>
+        <v>0.9999998983739596</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>DR-195</t>
+          <t>LSC-12</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -716,7 +716,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -726,19 +726,19 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9995526880205594</v>
+        <v>0.9932125113745492</v>
       </c>
       <c r="G10" t="n">
-        <v>6.905400780465352e-45</v>
+        <v>0.006787488625450535</v>
       </c>
       <c r="H10" t="n">
-        <v>0.000447311979440594</v>
+        <v>2.805908824159893e-16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>DR-197</t>
+          <t>SCR-04</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -746,63 +746,63 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>2.242107158608158e-08</v>
+        <v>0.5564807001718851</v>
       </c>
       <c r="G11" t="n">
-        <v>6.625979709576053e-11</v>
+        <v>0.4435192998281149</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9999999775126686</v>
+        <v>4.801381504122917e-34</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>DR-202</t>
+          <t>SCR-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>3.061297653740543e-05</v>
+        <v>0.9927384464683222</v>
       </c>
       <c r="G12" t="n">
-        <v>2.487595470297807e-16</v>
+        <v>0.007261553531677714</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9999693870234623</v>
+        <v>5.722586475372274e-39</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>DR-204</t>
+          <t>DR-141</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -810,55 +810,55 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>5.173938765476805e-07</v>
+        <v>0.8144072128536445</v>
       </c>
       <c r="G13" t="n">
-        <v>1.34074020420173e-14</v>
+        <v>0.1855927871463556</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9999994826061099</v>
+        <v>2.750203486991994e-22</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>DR-205</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>3</v>
       </c>
       <c r="E14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0004766501040335004</v>
+        <v>1.384935410666222e-18</v>
       </c>
       <c r="G14" t="n">
-        <v>9.499084300941895e-24</v>
+        <v>7.699292622681426e-24</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9995233498959665</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>DR-206</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -866,33 +866,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>1.039839269974045e-16</v>
+        <v>0.9994141993509844</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9992839879545359</v>
+        <v>0.0005858006490154728</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0007160120454640274</v>
+        <v>1.04066055875601e-28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>DR-207</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9999829829335232</v>
+        <v>0.2686349931789204</v>
       </c>
       <c r="G16" t="n">
-        <v>1.460641766532878e-48</v>
+        <v>0.7313650068210796</v>
       </c>
       <c r="H16" t="n">
-        <v>1.701706647690897e-05</v>
+        <v>3.95524463373581e-32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>DR-208</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -926,7 +926,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -936,23 +936,23 @@
         <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>6.090220025578483e-06</v>
+        <v>6.171165691474373e-25</v>
       </c>
       <c r="G17" t="n">
-        <v>2.819620327627155e-20</v>
+        <v>2.204585651314021e-29</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9999939097799744</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>DR-209</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -960,85 +960,85 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" t="b">
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0004537031833414897</v>
+        <v>0.7828238470897687</v>
       </c>
       <c r="G18" t="n">
-        <v>6.399441533796586e-24</v>
+        <v>0.2171761529102314</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9995462968166585</v>
+        <v>8.852378618564675e-38</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>DR-15</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>3</v>
       </c>
       <c r="E19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0006132722338878922</v>
+        <v>6.514406329158804e-32</v>
       </c>
       <c r="G19" t="n">
-        <v>2.10242000719677e-22</v>
+        <v>1.008193000469149e-36</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9993867277661121</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>DR-17</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20" t="b">
         <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>4.452045330423855e-09</v>
+        <v>0.9324216841645221</v>
       </c>
       <c r="G20" t="n">
-        <v>3.624817801607503e-07</v>
+        <v>0.06757831583547791</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9999996330661746</v>
+        <v>1.750332447628084e-22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>DR-18</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1056,79 +1056,79 @@
         <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9811234885426894</v>
+        <v>0.9079011008008311</v>
       </c>
       <c r="G21" t="n">
-        <v>1.898841446727086e-36</v>
+        <v>0.09209889919916886</v>
       </c>
       <c r="H21" t="n">
-        <v>0.01887651145731052</v>
+        <v>3.841795911905917e-25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>DR-19</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22" t="b">
         <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3652250162064756</v>
+        <v>0.9812250301269169</v>
       </c>
       <c r="G22" t="n">
-        <v>1.171446580014517e-26</v>
+        <v>0.01877496987174898</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6347749837935245</v>
+        <v>1.334128842077602e-12</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>DR-20</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" t="b">
         <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0002779462404193438</v>
+        <v>0.9976631683622095</v>
       </c>
       <c r="G23" t="n">
-        <v>1.750992354023995e-17</v>
+        <v>0.002336831637790527</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9997220537595806</v>
+        <v>5.604936139623648e-31</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>DR-23</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1136,29 +1136,29 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>8.408178932678543e-07</v>
+        <v>0.9965227762286866</v>
       </c>
       <c r="G24" t="n">
-        <v>2.045946738789998e-14</v>
+        <v>0.003477223771313482</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9999991591820863</v>
+        <v>5.535327606021869e-35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>DR-38</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1176,19 +1176,19 @@
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>0.999999599309811</v>
+        <v>0.9999942000004347</v>
       </c>
       <c r="G25" t="n">
-        <v>2.433602805658487e-51</v>
+        <v>5.799999565323212e-06</v>
       </c>
       <c r="H25" t="n">
-        <v>4.006901890331989e-07</v>
+        <v>6.17960879420007e-56</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>DR-40</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1206,23 +1206,23 @@
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9434858434122564</v>
+        <v>0.9908467521783334</v>
       </c>
       <c r="G26" t="n">
-        <v>3.4861163351444e-32</v>
+        <v>0.009153247821666674</v>
       </c>
       <c r="H26" t="n">
-        <v>0.05651415658774357</v>
+        <v>5.439767626469993e-44</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>DR-44</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1230,29 +1230,29 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27" t="b">
         <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>0.07829304867839018</v>
+        <v>0.9999468217984029</v>
       </c>
       <c r="G27" t="n">
-        <v>1.097069786508977e-28</v>
+        <v>5.317820159724976e-05</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9217069513216098</v>
+        <v>2.156390026592585e-39</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>DR-45</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1263,26 +1263,26 @@
         <v>1</v>
       </c>
       <c r="E28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9994961593998823</v>
+        <v>0.9999767168786988</v>
       </c>
       <c r="G28" t="n">
-        <v>5.507451050981829e-41</v>
+        <v>2.32831212574836e-05</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0005038406001176753</v>
+        <v>4.370191390194611e-14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>DR-48</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1290,25 +1290,25 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E29" t="b">
         <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0008733383837855163</v>
+        <v>0.9914373619450524</v>
       </c>
       <c r="G29" t="n">
-        <v>2.789955739355438e-22</v>
+        <v>0.008562638054947593</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9991266616162144</v>
+        <v>1.869073835460701e-36</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>DR-49</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1326,53 +1326,53 @@
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9098973748970235</v>
+        <v>0.9931130852752955</v>
       </c>
       <c r="G30" t="n">
-        <v>6.443919329298773e-33</v>
+        <v>0.006886914724704428</v>
       </c>
       <c r="H30" t="n">
-        <v>0.09010262510297665</v>
+        <v>1.764600210286172e-36</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>DR-50</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E31" t="b">
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>0.05670444379523303</v>
+        <v>0.9922950453301113</v>
       </c>
       <c r="G31" t="n">
-        <v>2.884218623747994e-25</v>
+        <v>0.007704954669888721</v>
       </c>
       <c r="H31" t="n">
-        <v>0.943295556204767</v>
+        <v>3.726178815735047e-40</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>DR-51</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1380,59 +1380,59 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E32" t="b">
         <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>4.922783384216739e-05</v>
+        <v>0.9916268338029839</v>
       </c>
       <c r="G32" t="n">
-        <v>2.497697121293739e-17</v>
+        <v>0.008373166197016214</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9999507721661578</v>
+        <v>2.604814110555107e-32</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>DR-53</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E33" t="b">
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>0.002690981243843975</v>
+        <v>0.9220594925296278</v>
       </c>
       <c r="G33" t="n">
-        <v>5.35945526971653e-22</v>
+        <v>0.0779405074703723</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9973090187561561</v>
+        <v>9.649062903675408e-23</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>DR-55</t>
+          <t>LSC-30</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1440,25 +1440,25 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E34" t="b">
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0001916344552161711</v>
+        <v>0.9941010473697466</v>
       </c>
       <c r="G34" t="n">
-        <v>9.342885039606009e-26</v>
+        <v>0.005898952630253456</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9998083655447838</v>
+        <v>3.61365446238452e-30</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>DR-56</t>
+          <t>LSC-32</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1466,59 +1466,59 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8703391515563766</v>
+        <v>0.002702766393568608</v>
       </c>
       <c r="G35" t="n">
-        <v>6.080854167637393e-31</v>
+        <v>0.9972972336064313</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1296608484436232</v>
+        <v>4.339816498880127e-31</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>DR-59</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E36" t="b">
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>9.657027928612704e-07</v>
+        <v>0.6424133429665312</v>
       </c>
       <c r="G36" t="n">
-        <v>7.661194044044215e-14</v>
+        <v>0.3575866570334688</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9999990342971306</v>
+        <v>2.381993386855221e-22</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>LSC-09</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1536,23 +1536,23 @@
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9998962976373398</v>
+        <v>0.9860409183750889</v>
       </c>
       <c r="G37" t="n">
-        <v>2.124781701632662e-52</v>
+        <v>0.01395908162491114</v>
       </c>
       <c r="H37" t="n">
-        <v>0.000103702362660273</v>
+        <v>3.444560014487434e-30</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>DR-140</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1560,29 +1560,29 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E38" t="b">
         <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>0.001473973451602997</v>
+        <v>0.995909569682116</v>
       </c>
       <c r="G38" t="n">
-        <v>1.166376182036637e-21</v>
+        <v>0.004090430317884105</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9985260265483971</v>
+        <v>1.370873129315487e-38</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>LSC-17</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1590,25 +1590,25 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.100788981938709</v>
+        <v>0.8794134971166455</v>
       </c>
       <c r="G39" t="n">
-        <v>1.388523814739045e-26</v>
+        <v>0.1205865028833544</v>
       </c>
       <c r="H39" t="n">
-        <v>0.899211018061291</v>
+        <v>5.774297498596669e-30</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>LSC-24</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1626,23 +1626,23 @@
         <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9938703069845746</v>
+        <v>0.9858915970996538</v>
       </c>
       <c r="G40" t="n">
-        <v>5.893127491478644e-39</v>
+        <v>0.01410840290034625</v>
       </c>
       <c r="H40" t="n">
-        <v>0.006129693015425484</v>
+        <v>2.858856496962257e-31</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>LSC-53</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1653,76 +1653,586 @@
         <v>1</v>
       </c>
       <c r="E41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9921625352196256</v>
+        <v>0.9330663222691633</v>
       </c>
       <c r="G41" t="n">
-        <v>2.810641108415308e-37</v>
+        <v>0.06693367773083669</v>
       </c>
       <c r="H41" t="n">
-        <v>0.007837464780374458</v>
+        <v>8.105350641213544e-28</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>DR-144</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>1</v>
       </c>
       <c r="E42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9999999999605622</v>
+        <v>0.9308528032707329</v>
       </c>
       <c r="G42" t="n">
-        <v>1.64577733998495e-58</v>
+        <v>0.06914719672926693</v>
       </c>
       <c r="H42" t="n">
-        <v>3.943772620685546e-11</v>
+        <v>2.31658204927648e-24</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
+          <t>LSC-45</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.6499774665280567</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.3500225334719434</v>
+      </c>
+      <c r="H43" t="n">
+        <v>4.664395687976026e-43</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>LSC-47</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaWeak</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" t="b">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.03047746694880172</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.9695225330511983</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.013467356756302e-42</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>LSC-48</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="b">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.7450118025908699</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.2549881974091301</v>
+      </c>
+      <c r="H45" t="n">
+        <v>3.004095904865443e-42</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>LSC-53</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="b">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.994740692737531</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.00525930726246916</v>
+      </c>
+      <c r="H46" t="n">
+        <v>3.542956477287938e-36</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>LSC-55</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="b">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.8522487360710671</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.147751263928933</v>
+      </c>
+      <c r="H47" t="n">
+        <v>7.383350965450501e-42</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>LSC-56</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="b">
+        <v>1</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.9695368636876834</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.0304631363123167</v>
+      </c>
+      <c r="H48" t="n">
+        <v>3.238116375935817e-31</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>LSC-57</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaWeak</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="b">
+        <v>1</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.918986457535833</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.08101354246416707</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2.956104273265506e-36</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>LSC-58</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaWeak</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.5999093527367141</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.400090647263286</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1.605442850051178e-31</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>LSC-59</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" t="b">
+        <v>1</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.399678313547528</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.600321686452472</v>
+      </c>
+      <c r="H51" t="n">
+        <v>3.237111742680726e-33</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>LSC-60</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>EnvWeak_TaxaWeak</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="b">
+        <v>1</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.8870339748969177</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.1129660251030822</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1.845510896678766e-28</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>LSC-62</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="b">
+        <v>1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.9921407358770273</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.007859264122972592</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2.280205109306539e-22</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>SCR-08</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="b">
+        <v>1</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.9807749478333576</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.01922505216664237</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1.278246593898778e-36</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>DR-144</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>EnvWeak_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" t="b">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>8.05497874919727e-24</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1.513646066676685e-29</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>DR-145</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="b">
+        <v>1</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.9962283222779791</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.003771677722021046</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1.206647137586476e-31</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>SCR-09</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>EnvWeak_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="b">
+        <v>1</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.6036338423070458</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.3963661576929542</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1.492633568152601e-34</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>DR-156</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.9909751931236458</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.009024806876354151</v>
+      </c>
+      <c r="H58" t="n">
+        <v>3.987718882843544e-36</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
           <t>DR-157</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" t="inlineStr">
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="inlineStr">
         <is>
           <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="b">
+        <v>1</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.9983342227881874</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.001665777211812657</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1.933211459891826e-33</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>DR-159</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>EnvWeak_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
         <v>3</v>
       </c>
-      <c r="E43" t="b">
+      <c r="E60" t="b">
         <v>0</v>
       </c>
-      <c r="F43" t="n">
-        <v>0.4133489369190837</v>
-      </c>
-      <c r="G43" t="n">
-        <v>5.143367635951179e-28</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.5866510630809163</v>
+      <c r="F60" t="n">
+        <v>1.272057524040031e-18</v>
+      </c>
+      <c r="G60" t="n">
+        <v>8.360190676480537e-23</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/LDA_Method/ModelS_XSupport/tables/cross_support_site_predictions.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelS_XSupport/tables/cross_support_site_predictions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,11 +456,6 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>LDA_Cluster 2</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
           <t>LDA_Cluster 3</t>
         </is>
       </c>
@@ -476,7 +471,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,13 +481,10 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.998752729442381</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001247270557618951</v>
-      </c>
-      <c r="H2" t="n">
-        <v>9.474796039594086e-27</v>
+        <v>2.659608448613661e-44</v>
       </c>
     </row>
     <row r="3">
@@ -506,7 +498,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -516,13 +508,10 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8704088668453721</v>
+        <v>0.999999748385011</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0001944975811842939</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.1293966355734435</v>
+        <v>2.516149889773066e-07</v>
       </c>
     </row>
     <row r="4">
@@ -532,7 +521,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -540,19 +529,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0003761675276060683</v>
+        <v>0.9999999999998967</v>
       </c>
       <c r="G4" t="n">
-        <v>1.937770785980285e-06</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9996218947016079</v>
+        <v>1.03279172623032e-13</v>
       </c>
     </row>
     <row r="5">
@@ -576,13 +562,10 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9964455835682403</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003554416431759609</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.055349579375182e-32</v>
+        <v>3.907690364409713e-83</v>
       </c>
     </row>
     <row r="6">
@@ -606,12 +589,9 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>2.124234677395084e-34</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1.106606378344374e-38</v>
-      </c>
-      <c r="H6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -622,27 +602,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9386343260964012</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06136567390359882</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2.843174666881501e-31</v>
+        <v>6.713620566580402e-76</v>
       </c>
     </row>
     <row r="8">
@@ -666,13 +643,10 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>1.178100880455004e-14</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>9.306263433931688e-19</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.9999999999999882</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -686,23 +660,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>1.015638210643479e-07</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>6.221921825830707e-11</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.9999998983739596</v>
+        <v>5.886533146129404e-33</v>
       </c>
     </row>
     <row r="10">
@@ -712,27 +683,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9932125113745492</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.006787488625450535</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2.805908824159893e-16</v>
+        <v>1.108468348357597e-69</v>
       </c>
     </row>
     <row r="11">
@@ -746,7 +714,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -756,13 +724,10 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5564807001718851</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4435192998281149</v>
-      </c>
-      <c r="H11" t="n">
-        <v>4.801381504122917e-34</v>
+        <v>2.277952280292786e-83</v>
       </c>
     </row>
     <row r="12">
@@ -786,79 +751,70 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9927384464683222</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.007261553531677714</v>
-      </c>
-      <c r="H12" t="n">
-        <v>5.722586475372274e-39</v>
+        <v>6.07737193615386e-89</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>DR-141</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EnvWeak_TaxaWeak</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>3</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>EnvWeak_TaxaWeak</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8144072128536445</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1855927871463556</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2.750203486991994e-22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>DR-143</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>1.384935410666222e-18</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>7.699292622681426e-24</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
+        <v>2.443547167939101e-80</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>SCR-11</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -866,7 +822,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -876,83 +832,74 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9994141993509844</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0005858006490154728</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.04066055875601e-28</v>
+        <v>1.869532087778915e-87</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SCR-14</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2686349931789204</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7313650068210796</v>
-      </c>
-      <c r="H16" t="n">
-        <v>3.95524463373581e-32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>SCR-17</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>6.171165691474373e-25</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>2.204585651314021e-29</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1</v>
+        <v>1.140863131935348e-90</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>SCR-18</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -960,55 +907,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" t="b">
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7828238470897687</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2171761529102314</v>
-      </c>
-      <c r="H18" t="n">
-        <v>8.852378618564675e-38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>SCR-19</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" t="b">
         <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>6.514406329158804e-32</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>1.008193000469149e-36</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1</v>
+        <v>5.17416097708262e-57</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>SCR-20</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1016,7 +957,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1026,19 +967,16 @@
         <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9324216841645221</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>0.06757831583547791</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.750332447628084e-22</v>
+        <v>4.032958337046771e-63</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>LSC-14</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1046,7 +984,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1056,19 +994,16 @@
         <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9079011008008311</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>0.09209889919916886</v>
-      </c>
-      <c r="H21" t="n">
-        <v>3.841795911905917e-25</v>
+        <v>3.770049886913116e-70</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>LSC-15</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1076,7 +1011,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1086,19 +1021,16 @@
         <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9812250301269169</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0.01877496987174898</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.334128842077602e-12</v>
+        <v>2.537588020841055e-65</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>LSC-16</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1116,19 +1048,16 @@
         <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9976631683622095</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>0.002336831637790527</v>
-      </c>
-      <c r="H23" t="n">
-        <v>5.604936139623648e-31</v>
+        <v>2.941772218398596e-88</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>LSC-17</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1136,7 +1065,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1146,19 +1075,16 @@
         <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9965227762286866</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>0.003477223771313482</v>
-      </c>
-      <c r="H24" t="n">
-        <v>5.535327606021869e-35</v>
+        <v>5.742403049017179e-117</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>LSC-18</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1166,7 +1092,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1176,19 +1102,16 @@
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9999942000004347</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>5.799999565323212e-06</v>
-      </c>
-      <c r="H25" t="n">
-        <v>6.17960879420007e-56</v>
+        <v>4.359492981552906e-100</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>LSC-19</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1206,79 +1129,70 @@
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9908467521783334</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>0.009153247821666674</v>
-      </c>
-      <c r="H26" t="n">
-        <v>5.439767626469993e-44</v>
+        <v>5.749436212529882e-88</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>LSC-22</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>1</v>
       </c>
       <c r="E27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9999468217984029</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>5.317820159724976e-05</v>
-      </c>
-      <c r="H27" t="n">
-        <v>2.156390026592585e-39</v>
+        <v>1.265753830306269e-66</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>LSC-23</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>1</v>
       </c>
       <c r="E28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9999767168786988</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>2.32831212574836e-05</v>
-      </c>
-      <c r="H28" t="n">
-        <v>4.370191390194611e-14</v>
+        <v>9.470995508867851e-91</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>LSC-24</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1296,19 +1210,16 @@
         <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9914373619450524</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.008562638054947593</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1.869073835460701e-36</v>
+        <v>1.70723894154804e-86</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>LSC-25</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1326,19 +1237,16 @@
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9931130852752955</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0.006886914724704428</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1.764600210286172e-36</v>
+        <v>3.304719503168349e-91</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>LSC-26</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1356,49 +1264,43 @@
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9922950453301113</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>0.007704954669888721</v>
-      </c>
-      <c r="H31" t="n">
-        <v>3.726178815735047e-40</v>
+        <v>2.267479240546902e-86</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>LSC-27</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>1</v>
       </c>
       <c r="E32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9916268338029839</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>0.008373166197016214</v>
-      </c>
-      <c r="H32" t="n">
-        <v>2.604814110555107e-32</v>
+        <v>2.834082512345294e-58</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>SCR-06</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1406,7 +1308,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1416,19 +1318,16 @@
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9220594925296278</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0779405074703723</v>
-      </c>
-      <c r="H33" t="n">
-        <v>9.649062903675408e-23</v>
+        <v>3.605067691707584e-83</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>LSC-30</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1446,19 +1345,16 @@
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9941010473697466</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>0.005898952630253456</v>
-      </c>
-      <c r="H34" t="n">
-        <v>3.61365446238452e-30</v>
+        <v>1.321885958360466e-79</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>LSC-32</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1466,59 +1362,53 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>0.002702766393568608</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9972972336064313</v>
-      </c>
-      <c r="H35" t="n">
-        <v>4.339816498880127e-31</v>
+        <v>1.795703671174096e-87</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>LSC-37</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>1</v>
       </c>
       <c r="E36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6424133429665312</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3575866570334688</v>
-      </c>
-      <c r="H36" t="n">
-        <v>2.381993386855221e-22</v>
+        <v>1.343373760199249e-80</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>LSC-38</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1526,7 +1416,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1536,49 +1426,43 @@
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9860409183750889</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>0.01395908162491114</v>
-      </c>
-      <c r="H37" t="n">
-        <v>3.444560014487434e-30</v>
+        <v>1.621627684530572e-82</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>LSC-39</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>1</v>
       </c>
       <c r="E38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.995909569682116</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0.004090430317884105</v>
-      </c>
-      <c r="H38" t="n">
-        <v>1.370873129315487e-38</v>
+        <v>3.536021665922123e-81</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>LSC-40</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1586,7 +1470,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1596,19 +1480,16 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8794134971166455</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1205865028833544</v>
-      </c>
-      <c r="H39" t="n">
-        <v>5.774297498596669e-30</v>
+        <v>3.640943162817839e-77</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>LSC-41</t>
+          <t>LSC-45</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1616,7 +1497,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1626,79 +1507,70 @@
         <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9858915970996538</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>0.01410840290034625</v>
-      </c>
-      <c r="H40" t="n">
-        <v>2.858856496962257e-31</v>
+        <v>3.395024674866315e-120</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>LSC-42</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>1</v>
       </c>
       <c r="E41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9330663222691633</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>0.06693367773083669</v>
-      </c>
-      <c r="H41" t="n">
-        <v>8.105350641213544e-28</v>
+        <v>2.148451556055198e-86</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>LSC-43</t>
+          <t>LSC-55</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>1</v>
       </c>
       <c r="E42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9308528032707329</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>0.06914719672926693</v>
-      </c>
-      <c r="H42" t="n">
-        <v>2.31658204927648e-24</v>
+        <v>1.653234063907241e-114</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>LSC-45</t>
+          <t>LSC-56</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1706,7 +1578,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1716,19 +1588,16 @@
         <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>0.6499774665280567</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>0.3500225334719434</v>
-      </c>
-      <c r="H43" t="n">
-        <v>4.664395687976026e-43</v>
+        <v>4.684503877960972e-91</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>LSC-47</t>
+          <t>LSC-57</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1736,29 +1605,26 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.03047746694880172</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>0.9695225330511983</v>
-      </c>
-      <c r="H44" t="n">
-        <v>1.013467356756302e-42</v>
+        <v>1.084152831942607e-94</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>LSC-48</t>
+          <t>LSC-58</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1766,7 +1632,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1776,79 +1642,70 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0.7450118025908699</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>0.2549881974091301</v>
-      </c>
-      <c r="H45" t="n">
-        <v>3.004095904865443e-42</v>
+        <v>1.644487284740848e-75</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>LSC-53</t>
+          <t>LSC-59</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D46" t="n">
         <v>1</v>
       </c>
       <c r="E46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0.994740692737531</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>0.00525930726246916</v>
-      </c>
-      <c r="H46" t="n">
-        <v>3.542956477287938e-36</v>
+        <v>4.975011334829153e-74</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>LSC-55</t>
+          <t>LSC-60</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D47" t="n">
         <v>1</v>
       </c>
       <c r="E47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0.8522487360710671</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>0.147751263928933</v>
-      </c>
-      <c r="H47" t="n">
-        <v>7.383350965450501e-42</v>
+        <v>3.805514365852717e-84</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>LSC-56</t>
+          <t>LSC-62</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1856,7 +1713,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -1866,19 +1723,16 @@
         <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9695368636876834</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0304631363123167</v>
-      </c>
-      <c r="H48" t="n">
-        <v>3.238116375935817e-31</v>
+        <v>1.094627204448849e-59</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>LSC-57</t>
+          <t>SCR-08</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1886,7 +1740,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -1896,19 +1750,16 @@
         <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>0.918986457535833</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>0.08101354246416707</v>
-      </c>
-      <c r="H49" t="n">
-        <v>2.956104273265506e-36</v>
+        <v>7.868852144484467e-90</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>LSC-58</t>
+          <t>DR-144</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -1916,33 +1767,30 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0.5999093527367141</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0.400090647263286</v>
-      </c>
-      <c r="H50" t="n">
-        <v>1.605442850051178e-31</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>LSC-59</t>
+          <t>DR-145</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1950,25 +1798,22 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51" t="b">
         <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>0.399678313547528</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>0.600321686452472</v>
-      </c>
-      <c r="H51" t="n">
-        <v>3.237111742680726e-33</v>
+        <v>1.17018341308291e-70</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>LSC-60</t>
+          <t>SCR-09</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -1976,7 +1821,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -1986,19 +1831,16 @@
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>0.8870339748969177</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>0.1129660251030822</v>
-      </c>
-      <c r="H52" t="n">
-        <v>1.845510896678766e-28</v>
+        <v>2.119077035752054e-89</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>LSC-62</t>
+          <t>DR-159</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2006,232 +1848,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9921407358770273</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0.007859264122972592</v>
-      </c>
-      <c r="H53" t="n">
-        <v>2.280205109306539e-22</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>SCR-08</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaStrong</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" t="b">
-        <v>1</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0.9807749478333576</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0.01922505216664237</v>
-      </c>
-      <c r="H54" t="n">
-        <v>1.278246593898778e-36</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>DR-144</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>EnvWeak_TaxaStrong</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>3</v>
-      </c>
-      <c r="E55" t="b">
-        <v>0</v>
-      </c>
-      <c r="F55" t="n">
-        <v>8.05497874919727e-24</v>
-      </c>
-      <c r="G55" t="n">
-        <v>1.513646066676685e-29</v>
-      </c>
-      <c r="H55" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>DR-145</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaStrong</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" t="b">
-        <v>1</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0.9962283222779791</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0.003771677722021046</v>
-      </c>
-      <c r="H56" t="n">
-        <v>1.206647137586476e-31</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>SCR-09</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>EnvWeak_TaxaStrong</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" t="b">
-        <v>1</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0.6036338423070458</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0.3963661576929542</v>
-      </c>
-      <c r="H57" t="n">
-        <v>1.492633568152601e-34</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>DR-156</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>1</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaStrong</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" t="b">
-        <v>1</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0.9909751931236458</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0.009024806876354151</v>
-      </c>
-      <c r="H58" t="n">
-        <v>3.987718882843544e-36</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>DR-157</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>1</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>EnvStrong_TaxaWeak</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" t="b">
-        <v>1</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0.9983342227881874</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0.001665777211812657</v>
-      </c>
-      <c r="H59" t="n">
-        <v>1.933211459891826e-33</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>DR-159</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>1</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>EnvWeak_TaxaStrong</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>3</v>
-      </c>
-      <c r="E60" t="b">
-        <v>0</v>
-      </c>
-      <c r="F60" t="n">
-        <v>1.272057524040031e-18</v>
-      </c>
-      <c r="G60" t="n">
-        <v>8.360190676480537e-23</v>
-      </c>
-      <c r="H60" t="n">
         <v>1</v>
       </c>
     </row>

--- a/results/02_taxa_assemblage/LDA_Method/ModelS_XSupport/tables/cross_support_site_predictions.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelS_XSupport/tables/cross_support_site_predictions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -484,7 +484,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>2.659608448613661e-44</v>
+        <v>1.173285790160116e-42</v>
       </c>
     </row>
     <row r="3">
@@ -498,20 +498,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.999999748385011</v>
+        <v>0.06018345541915215</v>
       </c>
       <c r="G3" t="n">
-        <v>2.516149889773066e-07</v>
+        <v>0.9398165445808478</v>
       </c>
     </row>
     <row r="4">
@@ -521,24 +521,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9999999999998967</v>
+        <v>1.590266880402424e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>1.03279172623032e-13</v>
+        <v>0.999999840973312</v>
       </c>
     </row>
     <row r="5">
@@ -552,7 +552,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -565,7 +565,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>3.907690364409713e-83</v>
+        <v>4.124391140161618e-55</v>
       </c>
     </row>
     <row r="6">
@@ -602,24 +602,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>6.713620566580402e-76</v>
+        <v>9.536429863298484e-52</v>
       </c>
     </row>
     <row r="8">
@@ -660,20 +660,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>2.354512638669259e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>5.886533146129404e-33</v>
+        <v>0.9999764548736133</v>
       </c>
     </row>
     <row r="10">
@@ -683,24 +683,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>1.108468348357597e-69</v>
+        <v>4.569839137977101e-21</v>
       </c>
     </row>
     <row r="11">
@@ -727,7 +727,7 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>2.277952280292786e-83</v>
+        <v>4.344531674669104e-56</v>
       </c>
     </row>
     <row r="12">
@@ -754,17 +754,17 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>6.07737193615386e-89</v>
+        <v>6.065683575088284e-61</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>DR-143</t>
+          <t>DR-141</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -772,49 +772,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>7.083028421538855e-43</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>SCR-11</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2.443547167939101e-80</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>SCR-14</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -822,7 +822,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -835,71 +835,71 @@
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>1.869532087778915e-87</v>
+        <v>4.648658794846538e-43</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SCR-17</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" t="b">
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>9.82261127684357e-57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>SCR-18</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.140863131935348e-90</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>SCR-19</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -907,49 +907,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" t="b">
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>8.918061151127495e-64</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>SCR-20</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19" t="b">
         <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>5.17416097708262e-57</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>LSC-14</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -957,7 +957,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -970,13 +970,13 @@
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>4.032958337046771e-63</v>
+        <v>4.449461879022846e-39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>LSC-15</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -984,7 +984,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -997,13 +997,13 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>3.770049886913116e-70</v>
+        <v>4.191204858781106e-46</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>LSC-16</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1024,13 +1024,13 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>2.537588020841055e-65</v>
+        <v>4.697180364627337e-24</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>LSC-17</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1051,13 +1051,13 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>2.941772218398596e-88</v>
+        <v>2.215633796328156e-46</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>LSC-18</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1078,13 +1078,13 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>5.742403049017179e-117</v>
+        <v>1.013084909548486e-56</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>LSC-19</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>4.359492981552906e-100</v>
+        <v>2.315864907708304e-88</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>LSC-22</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1132,67 +1132,67 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>5.749436212529882e-88</v>
+        <v>4.36966033393382e-70</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>LSC-23</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>1</v>
       </c>
       <c r="E27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>1.265753830306269e-66</v>
+        <v>5.436187191726753e-61</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>LSC-24</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>1</v>
       </c>
       <c r="E28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>9.470995508867851e-91</v>
+        <v>1.579578520516198e-17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>LSC-25</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1213,13 +1213,13 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>1.70723894154804e-86</v>
+        <v>7.906582940909219e-57</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>LSC-26</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1240,13 +1240,13 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>3.304719503168349e-91</v>
+        <v>2.716016644410713e-56</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>LSC-27</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1267,40 +1267,40 @@
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>2.267479240546902e-86</v>
+        <v>8.811067288206335e-61</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>SCR-06</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>1</v>
       </c>
       <c r="E32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>2.834082512345294e-58</v>
+        <v>6.85251636536889e-50</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>LSC-37</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1321,13 +1321,13 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>3.605067691707584e-83</v>
+        <v>1.39748241544708e-39</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>LSC-38</t>
+          <t>LSC-30</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1348,13 +1348,13 @@
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>1.321885958360466e-79</v>
+        <v>1.66830270326526e-52</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>LSC-39</t>
+          <t>LSC-32</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1375,40 +1375,40 @@
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>1.795703671174096e-87</v>
+        <v>4.726797552755686e-59</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>LSC-40</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>1</v>
       </c>
       <c r="E36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>1.343373760199249e-80</v>
+        <v>3.410682169904072e-44</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>LSC-41</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1429,40 +1429,40 @@
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>1.621627684530572e-82</v>
+        <v>1.633998697777528e-49</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>LSC-42</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>1</v>
       </c>
       <c r="E38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>3.536021665922123e-81</v>
+        <v>8.261291240886273e-58</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>LSC-43</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1483,13 +1483,13 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>3.640943162817839e-77</v>
+        <v>1.60716440849971e-49</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>LSC-45</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1510,67 +1510,67 @@
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>3.395024674866315e-120</v>
+        <v>1.932292759881871e-46</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>LSC-53</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>1</v>
       </c>
       <c r="E41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>2.148451556055198e-86</v>
+        <v>1.905814995064013e-45</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>LSC-55</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>1</v>
       </c>
       <c r="E42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>1.653234063907241e-114</v>
+        <v>1.567785390390113e-42</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>LSC-56</t>
+          <t>LSC-45</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1591,13 +1591,13 @@
         <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>4.684503877960972e-91</v>
+        <v>1.777031624077567e-75</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>LSC-57</t>
+          <t>LSC-47</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1618,13 +1618,13 @@
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>1.084152831942607e-94</v>
+        <v>3.319660230602048e-75</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>LSC-58</t>
+          <t>LSC-48</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1645,67 +1645,67 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>1.644487284740848e-75</v>
+        <v>2.930894244344258e-72</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>LSC-59</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaStrong</t>
         </is>
       </c>
       <c r="D46" t="n">
         <v>1</v>
       </c>
       <c r="E46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>4.975011334829153e-74</v>
+        <v>6.916880142174007e-55</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>LSC-60</t>
+          <t>LSC-55</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaWeak</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D47" t="n">
         <v>1</v>
       </c>
       <c r="E47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>3.805514365852717e-84</v>
+        <v>1.676130779701455e-70</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>LSC-62</t>
+          <t>LSC-56</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1726,13 +1726,13 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>1.094627204448849e-59</v>
+        <v>8.582824947717665e-51</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>SCR-08</t>
+          <t>LSC-57</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -1753,13 +1753,13 @@
         <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>7.868852144484467e-90</v>
+        <v>1.076714634396822e-57</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>DR-144</t>
+          <t>LSC-58</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -1767,53 +1767,53 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvStrong_TaxaWeak</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>1.241174180286148e-52</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>DR-145</t>
+          <t>LSC-59</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>EnvStrong_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D51" t="n">
         <v>1</v>
       </c>
       <c r="E51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>1.17018341308291e-70</v>
+        <v>2.036134186917154e-54</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>SCR-09</t>
+          <t>LSC-60</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>EnvWeak_TaxaStrong</t>
+          <t>EnvWeak_TaxaWeak</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -1834,33 +1834,222 @@
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>2.119077035752054e-89</v>
+        <v>2.784582011963818e-49</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
+          <t>LSC-62</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>EnvWeak_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="b">
+        <v>1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="n">
+        <v>4.430018410827687e-37</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>SCR-08</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="b">
+        <v>1</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="n">
+        <v>3.426849466591519e-58</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>DR-144</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>EnvWeak_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" t="b">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>DR-145</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaWeak</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="b">
+        <v>1</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2.670699200576066e-50</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>SCR-09</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>EnvWeak_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="b">
+        <v>1</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>7.151847494819296e-59</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>DR-156</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaStrong</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2.718185798961908e-54</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>DR-157</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>EnvStrong_TaxaWeak</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="b">
+        <v>1</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="n">
+        <v>4.562814881060605e-52</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
           <t>DR-159</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" t="inlineStr">
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="inlineStr">
         <is>
           <t>EnvWeak_TaxaStrong</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D60" t="n">
         <v>3</v>
       </c>
-      <c r="E53" t="b">
+      <c r="E60" t="b">
         <v>0</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F60" t="n">
         <v>0</v>
       </c>
-      <c r="G53" t="n">
+      <c r="G60" t="n">
         <v>1</v>
       </c>
     </row>
